--- a/examples/vi-du-studio/CMP-2609-gioi-thieu/CMP-2609-gioi-thieu.xlsx
+++ b/examples/vi-du-studio/CMP-2609-gioi-thieu/CMP-2609-gioi-thieu.xlsx
@@ -833,7 +833,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>C:\Users\DucNguyen\Code\agent-marketing-studio\examples\vi-du-studio\CMP-2609-gioi-thieu\campaign.md</t>
+          <t>vi-du-studio/CMP-2609-gioi-thieu/campaign.md</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">

--- a/examples/vi-du-studio/CMP-2609-gioi-thieu/CMP-2609-gioi-thieu.xlsx
+++ b/examples/vi-du-studio/CMP-2609-gioi-thieu/CMP-2609-gioi-thieu.xlsx
@@ -1529,7 +1529,9 @@
           <t>https://youtu.be/EXAMPLE0001</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>400</v>
+      </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
@@ -1605,7 +1607,9 @@
           <t>https://example.vn/blog/content/ai/vi-sao-agent-can-cong-cua-nguoi.html</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>400</v>
+      </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
@@ -1680,7 +1684,9 @@
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>30</v>
+      </c>
       <c r="Q4" t="inlineStr">
         <is>
           <t>2026-09-07T09:10:00</t>

--- a/examples/vi-du-studio/CMP-2609-gioi-thieu/CMP-2609-gioi-thieu.xlsx
+++ b/examples/vi-du-studio/CMP-2609-gioi-thieu/CMP-2609-gioi-thieu.xlsx
@@ -1093,7 +1093,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -1481,7 +1481,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GTX-001-yt</t>
+          <t>GTX-001-web</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1491,33 +1491,41 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>youtube</t>
+          <t>web_blog</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>youtube_video</t>
+          <t>blog_article</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>post:youtube_desc</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+          <t>post:blog_article</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Duyệt: mở bài đúng vấn đề, không hứa quá.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
@@ -1526,25 +1534,21 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://youtu.be/EXAMPLE0001</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>400</v>
-      </c>
+          <t>https://example.vn/blog/content/ai/vi-sao-agent-can-cong-cua-nguoi.html</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:00:00</t>
+          <t>2026-09-05T00:18:09+00:00</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>214</v>
-      </c>
-      <c r="T2" t="n">
-        <v>19</v>
-      </c>
+        <v>531</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
@@ -1552,14 +1556,14 @@
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-05T00:18:09+00:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GTX-001-web</t>
+          <t>GTX-001-yt</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1569,33 +1573,41 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>web_blog</t>
+          <t>youtube</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>blog_article</t>
+          <t>youtube_video</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>post:blog_article</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+          <t>post:youtube_desc</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Duyệt: đủ nguồn, phần phản biện đứng được.</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
@@ -1604,23 +1616,25 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://example.vn/blog/content/ai/vi-sao-agent-can-cong-cua-nguoi.html</t>
+          <t>https://youtu.be/EXAMPLE0001</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-07T09:05:00</t>
+          <t>2026-09-05T00:18:09+00:00</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>531</v>
-      </c>
-      <c r="T3" t="inlineStr"/>
+        <v>214</v>
+      </c>
+      <c r="T3" t="n">
+        <v>19</v>
+      </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
@@ -1628,7 +1642,7 @@
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-05T00:18:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1659,19 +1673,27 @@
           <t>post:facebook_post</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>approved</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Duyệt: thân bài không có link, comment dẫn về bài dài.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
@@ -1683,13 +1705,13 @@
           <t>https://www.facebook.com/000000000000000/posts/111111111111111</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
-        <v>30</v>
-      </c>
+      <c r="O4" t="n">
+        <v>40</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-07T09:10:00</t>
+          <t>2026-09-05T00:18:09+00:00</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
@@ -1710,7 +1732,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-05T00:18:09+00:00</t>
         </is>
       </c>
     </row>
